--- a/M2_Statistica_&_Excel/W2_D1.xlsx
+++ b/M2_Statistica_&_Excel/W2_D1.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SZN\Desktop\EPICODE CORSO\esercizi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E43BBF4-5346-4E87-900B-A0004EFEDCAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB822322-8FC3-4498-A463-385FFF718652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B0536D41-C147-4827-AD61-53A4FD8EB59B}"/>
   </bookViews>
   <sheets>
-    <sheet name="Esercizi" sheetId="2" r:id="rId1"/>
+    <sheet name="Esercizi_1_2" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="camp">Esercizi!$A$2:$A$82</definedName>
-    <definedName name="campione">Esercizi!$A:$A</definedName>
-    <definedName name="sample">Esercizi!$A$1:$A$82</definedName>
+    <definedName name="camp">Esercizi_1_2!$A$2:$A$82</definedName>
+    <definedName name="campione">Esercizi_1_2!$A:$A</definedName>
+    <definedName name="sample">Esercizi_1_2!$A$1:$A$82</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="25">
   <si>
     <t>data</t>
   </si>
@@ -115,7 +115,10 @@
     <t>Esercizio 1.</t>
   </si>
   <si>
-    <t>notiamo come all'aumentare il numero di di dati nel campione diminuisce l'errore standard.</t>
+    <t xml:space="preserve">all'aumentare della confidenza più l'intervallo diventa più ampio e quindi più probabile, con più probabilità di includere il valore nell'intervallo. </t>
+  </si>
+  <si>
+    <t>all'aumentare dei dati del campione diminuisce l'intervallo di confidenza aumentando la probabilità che il valore ricada all'interno dell'intervallo.</t>
   </si>
 </sst>
 </file>
@@ -211,15 +214,6 @@
         <color indexed="64"/>
       </left>
       <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -239,11 +233,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -254,23 +261,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -279,15 +277,23 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -636,85 +642,85 @@
       <c r="A1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="16"/>
+      <c r="C1" s="13"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
-        <v>55</v>
-      </c>
-      <c r="B2" s="4" t="s">
+      <c r="A2" s="9">
+        <v>50.226791890560854</v>
+      </c>
+      <c r="B2" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="6" t="s">
+      <c r="C2" s="15"/>
+      <c r="D2" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="7"/>
+      <c r="E2" s="15"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
-        <v>49</v>
-      </c>
-      <c r="B3" s="5" t="s">
+      <c r="A3" s="9">
+        <v>49.929976818027036</v>
+      </c>
+      <c r="B3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="6">
         <f>AVERAGE(camp)</f>
-        <v>51.851851851851855</v>
-      </c>
-      <c r="D3" s="5" t="s">
+        <v>52.000000000000014</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="11">
+      <c r="E3" s="8">
         <v>0.95</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
-        <v>62</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="A4" s="9">
+        <v>50.56441257177115</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="6">
         <f>_xlfn.STDEV.P(camp)</f>
-        <v>8.3030726294043244</v>
-      </c>
-      <c r="D4" s="5" t="s">
+        <v>8.9442719099990313</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="9">
         <f>1-E3</f>
         <v>5.0000000000000044E-2</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
-        <v>42</v>
-      </c>
-      <c r="B5" s="5" t="s">
+      <c r="A5" s="9">
+        <v>58.942481756369347</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="7">
         <f>COUNT(camp)</f>
         <v>81</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="9">
         <f>_xlfn.CONFIDENCE.NORM(E4,C$4,C$5)</f>
-        <v>1.8081914794058622</v>
+        <v>1.9478278679479308</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
-        <v>53</v>
-      </c>
-      <c r="D6" s="5" t="s">
+      <c r="A6" s="9">
+        <v>50.396784945549271</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>1</v>
       </c>
       <c r="E6" s="3" t="s">
@@ -722,45 +728,45 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="3">
-        <v>61</v>
-      </c>
-      <c r="D7" s="5" t="s">
+      <c r="A7" s="9">
+        <v>36.286379359949052</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="9">
         <f>C$3+E5</f>
-        <v>53.660043331257718</v>
+        <v>53.947827867947943</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
-        <v>37</v>
-      </c>
-      <c r="D8" s="5" t="s">
+      <c r="A8" s="9">
+        <v>55.134435879789187</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="9">
         <f>C$3-E5</f>
-        <v>50.043660372445991</v>
-      </c>
-      <c r="F8" s="8" t="s">
+        <v>50.052172132052085</v>
+      </c>
+      <c r="F8" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="3">
-        <v>57</v>
+      <c r="A9" s="9">
+        <v>48.957182072262427</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="3">
-        <v>38</v>
+      <c r="A10" s="9">
+        <v>49.476150766501469</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="3">
-        <v>42</v>
+      <c r="A11" s="9">
+        <v>52.904881915646136</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>9</v>
@@ -768,45 +774,45 @@
       <c r="E11" s="2"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
-        <v>62</v>
-      </c>
-      <c r="D12" s="5" t="s">
+      <c r="A12" s="9">
+        <v>54.104090382977908</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="11">
+      <c r="E12" s="8">
         <v>0.9</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="3">
-        <v>54</v>
-      </c>
-      <c r="D13" s="5" t="s">
+      <c r="A13" s="9">
+        <v>63.697318749681642</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="9">
         <f>1-E12</f>
         <v>9.9999999999999978E-2</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="3">
-        <v>63</v>
-      </c>
-      <c r="D14" s="5" t="s">
+      <c r="A14" s="9">
+        <v>58.475344998307918</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="9">
         <f>_xlfn.CONFIDENCE.NORM(E13,C$4,C$5)</f>
-        <v>1.5174821254796884</v>
+        <v>1.6346686768446748</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="3">
-        <v>43</v>
-      </c>
-      <c r="D15" s="5" t="s">
+      <c r="A15" s="9">
+        <v>52.849485376484303</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>1</v>
       </c>
       <c r="E15" s="3" t="s">
@@ -814,45 +820,45 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="3">
-        <v>59</v>
-      </c>
-      <c r="D16" s="5" t="s">
+      <c r="A16" s="9">
+        <v>44.10541817230002</v>
+      </c>
+      <c r="D16" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E16" s="12">
+      <c r="E16" s="9">
         <f>C$3+E14</f>
-        <v>53.369333977331543</v>
+        <v>53.63466867684469</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="3">
-        <v>51</v>
-      </c>
-      <c r="D17" s="5" t="s">
+      <c r="A17" s="9">
+        <v>41.258740162316862</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E17" s="12">
+      <c r="E17" s="9">
         <f>C$3-E14</f>
-        <v>50.334369726372167</v>
-      </c>
-      <c r="F17" s="13" t="s">
+        <v>50.365331323155338</v>
+      </c>
+      <c r="F17" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="3">
-        <v>61</v>
+      <c r="A18" s="9">
+        <v>54.248767012923615</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="3">
-        <v>43</v>
+      <c r="A19" s="9">
+        <v>65.21699332041851</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="3">
-        <v>55</v>
+      <c r="A20" s="9">
+        <v>52.140235427658659</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>9</v>
@@ -860,45 +866,45 @@
       <c r="E20" s="2"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="3">
-        <v>58</v>
-      </c>
-      <c r="D21" s="5" t="s">
+      <c r="A21" s="9">
+        <v>50.615842670958195</v>
+      </c>
+      <c r="D21" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E21" s="11">
+      <c r="E21" s="8">
         <v>0.99</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="3">
-        <v>66</v>
-      </c>
-      <c r="D22" s="5" t="s">
+      <c r="A22" s="9">
+        <v>57.189117715029539</v>
+      </c>
+      <c r="D22" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E22" s="12">
+      <c r="E22" s="9">
         <f>1-E21</f>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="3">
-        <v>39</v>
-      </c>
-      <c r="D23" s="5" t="s">
+      <c r="A23" s="9">
+        <v>36.737661317417022</v>
+      </c>
+      <c r="D23" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E23" s="12">
+      <c r="E23" s="9">
         <f>_xlfn.CONFIDENCE.NORM(E22,C$4,C$5)</f>
-        <v>2.3763664209238304</v>
+        <v>2.5598797427427549</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="3">
-        <v>45</v>
-      </c>
-      <c r="D24" s="5" t="s">
+      <c r="A24" s="9">
+        <v>48.494241867318117</v>
+      </c>
+      <c r="D24" s="4" t="s">
         <v>1</v>
       </c>
       <c r="E24" s="3" t="s">
@@ -906,132 +912,135 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="3">
-        <v>54</v>
-      </c>
-      <c r="D25" s="5" t="s">
+      <c r="A25" s="9">
+        <v>56.76250156112075</v>
+      </c>
+      <c r="D25" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E25" s="12">
+      <c r="E25" s="9">
         <f>C$3+E23</f>
-        <v>54.228218272775685</v>
+        <v>54.559879742742766</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="3">
-        <v>64</v>
-      </c>
-      <c r="D26" s="5" t="s">
+      <c r="A26" s="9">
+        <v>60.708342916322337</v>
+      </c>
+      <c r="D26" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E26" s="12">
+      <c r="E26" s="9">
         <f>C$3-E23</f>
-        <v>49.475485430928025</v>
-      </c>
-      <c r="F26" s="8" t="s">
+        <v>49.440120257257263</v>
+      </c>
+      <c r="F26" s="5" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="3">
-        <v>50</v>
+      <c r="A27" s="9">
+        <v>49.232308051399457</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="3">
-        <v>62</v>
+      <c r="A28" s="9">
+        <v>55.590594470263071</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="3">
-        <v>40</v>
+      <c r="A29" s="9">
+        <v>54.268043423133321</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="3">
-        <v>52</v>
-      </c>
-      <c r="B30" s="14" t="s">
+      <c r="A30" s="9">
+        <v>59.770122547020328</v>
+      </c>
+      <c r="B30" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C30" s="15"/>
+      <c r="C30" s="11"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="3">
-        <v>43</v>
-      </c>
-      <c r="B31" s="4" t="s">
+      <c r="A31" s="9">
+        <v>40.243442443591881</v>
+      </c>
+      <c r="B31" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4" t="s">
+      <c r="C31" s="15"/>
+      <c r="D31" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="E31" s="4"/>
-      <c r="F31" s="8" t="s">
-        <v>23</v>
+      <c r="E31" s="15"/>
+      <c r="F31" s="5" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="3">
-        <v>55</v>
-      </c>
-      <c r="B32" s="5" t="s">
+      <c r="A32" s="9">
+        <v>57.56485331671076</v>
+      </c>
+      <c r="B32" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C32" s="9">
+      <c r="C32" s="6">
         <f>AVERAGE(camp)</f>
-        <v>51.851851851851855</v>
-      </c>
-      <c r="D32" s="5" t="s">
+        <v>52.000000000000014</v>
+      </c>
+      <c r="D32" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E32" s="11">
+      <c r="E32" s="8">
         <v>0.95</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="3">
-        <v>50</v>
-      </c>
-      <c r="B33" s="5" t="s">
+      <c r="A33" s="9">
+        <v>36.109536623799862</v>
+      </c>
+      <c r="B33" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C33" s="9">
+      <c r="C33" s="6">
         <f>_xlfn.STDEV.P(camp)</f>
-        <v>8.3030726294043244</v>
-      </c>
-      <c r="D33" s="5" t="s">
+        <v>8.9442719099990313</v>
+      </c>
+      <c r="D33" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E33" s="12">
+      <c r="E33" s="9">
         <f>1-E32</f>
         <v>5.0000000000000044E-2</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="3">
-        <v>57</v>
-      </c>
-      <c r="B34" s="5" t="s">
+      <c r="A34" s="9">
+        <v>24.722186211115726</v>
+      </c>
+      <c r="B34" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C34" s="10">
+      <c r="C34" s="7">
         <v>324</v>
       </c>
-      <c r="D34" s="5" t="s">
+      <c r="D34" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E34" s="12">
+      <c r="E34" s="9">
         <f>_xlfn.CONFIDENCE.NORM(E33,C$33,C$34)</f>
-        <v>0.90409573970293111</v>
+        <v>0.97391393397396542</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="3">
-        <v>47</v>
-      </c>
-      <c r="D35" s="5" t="s">
+      <c r="A35" s="9">
+        <v>45.459331262425799</v>
+      </c>
+      <c r="D35" s="4" t="s">
         <v>1</v>
       </c>
       <c r="E35" s="3" t="s">
@@ -1039,42 +1048,42 @@
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="3">
-        <v>50</v>
-      </c>
-      <c r="D36" s="5" t="s">
+      <c r="A36" s="9">
+        <v>42.277050756790402</v>
+      </c>
+      <c r="D36" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E36" s="12">
+      <c r="E36" s="9">
         <f>C$32+E34</f>
-        <v>52.755947591554786</v>
+        <v>52.973913933973982</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="3">
-        <v>49</v>
-      </c>
-      <c r="D37" s="5" t="s">
+      <c r="A37" s="9">
+        <v>60.735207324468298</v>
+      </c>
+      <c r="D37" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E37" s="12">
+      <c r="E37" s="9">
         <f>C$32-E34</f>
-        <v>50.947756112148923</v>
+        <v>51.026086066026046</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="3">
-        <v>55</v>
+      <c r="A38" s="9">
+        <v>58.553937907835945</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="3">
-        <v>48</v>
+      <c r="A39" s="9">
+        <v>39.15302040292223</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="3">
-        <v>49</v>
+      <c r="A40" s="9">
+        <v>60.440065714110027</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>9</v>
@@ -1082,45 +1091,45 @@
       <c r="E40" s="2"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="3">
-        <v>61</v>
-      </c>
-      <c r="D41" s="5" t="s">
+      <c r="A41" s="9">
+        <v>41.387090055799575</v>
+      </c>
+      <c r="D41" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E41" s="11">
+      <c r="E41" s="8">
         <v>0.9</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="3">
-        <v>52</v>
-      </c>
-      <c r="D42" s="5" t="s">
+      <c r="A42" s="9">
+        <v>50.822687728490145</v>
+      </c>
+      <c r="D42" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E42" s="12">
+      <c r="E42" s="9">
         <f>1-E41</f>
         <v>9.9999999999999978E-2</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="3">
-        <v>45</v>
-      </c>
-      <c r="D43" s="5" t="s">
+      <c r="A43" s="9">
+        <v>48.683555002704097</v>
+      </c>
+      <c r="D43" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E43" s="12">
+      <c r="E43" s="9">
         <f>_xlfn.CONFIDENCE.NORM(E42,C$33,C$34)</f>
-        <v>0.75874106273984421</v>
+        <v>0.81733433842233738</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="3">
-        <v>42</v>
-      </c>
-      <c r="D44" s="5" t="s">
+      <c r="A44" s="9">
+        <v>52.889791192960523</v>
+      </c>
+      <c r="D44" s="4" t="s">
         <v>1</v>
       </c>
       <c r="E44" s="3" t="s">
@@ -1128,42 +1137,42 @@
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="3">
-        <v>62</v>
-      </c>
-      <c r="D45" s="5" t="s">
+      <c r="A45" s="9">
+        <v>60.144158796196066</v>
+      </c>
+      <c r="D45" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E45" s="12">
+      <c r="E45" s="9">
         <f>C$32+E43</f>
-        <v>52.610592914591699</v>
+        <v>52.817334338422349</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="3">
-        <v>42</v>
-      </c>
-      <c r="D46" s="5" t="s">
+      <c r="A46" s="9">
+        <v>58.287626747943136</v>
+      </c>
+      <c r="D46" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E46" s="12">
+      <c r="E46" s="9">
         <f>C$32-E43</f>
-        <v>51.093110789112011</v>
+        <v>51.18266566157768</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="3">
-        <v>41</v>
+      <c r="A47" s="9">
+        <v>55.315396886806568</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="3">
-        <v>67</v>
+      <c r="A48" s="9">
+        <v>58.406445475682261</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="3">
-        <v>37</v>
+      <c r="A49" s="9">
+        <v>56.640219649852469</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>9</v>
@@ -1171,45 +1180,45 @@
       <c r="E49" s="2"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="3">
-        <v>47</v>
-      </c>
-      <c r="D50" s="5" t="s">
+      <c r="A50" s="9">
+        <v>45.252328701794092</v>
+      </c>
+      <c r="D50" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E50" s="11">
+      <c r="E50" s="8">
         <v>0.99</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="3">
-        <v>66</v>
-      </c>
-      <c r="D51" s="5" t="s">
+      <c r="A51" s="9">
+        <v>44.321236319486793</v>
+      </c>
+      <c r="D51" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E51" s="12">
+      <c r="E51" s="9">
         <f>1-E50</f>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="3">
-        <v>50</v>
-      </c>
-      <c r="D52" s="5" t="s">
+      <c r="A52" s="9">
+        <v>46.869814941349929</v>
+      </c>
+      <c r="D52" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E52" s="12">
+      <c r="E52" s="9">
         <f>_xlfn.CONFIDENCE.NORM(E51,C$33,C$34)</f>
-        <v>1.1881832104619152</v>
+        <v>1.2799398713713774</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="3">
-        <v>54</v>
-      </c>
-      <c r="D53" s="5" t="s">
+      <c r="A53" s="9">
+        <v>56.854841341588774</v>
+      </c>
+      <c r="D53" s="4" t="s">
         <v>1</v>
       </c>
       <c r="E53" s="3" t="s">
@@ -1217,162 +1226,162 @@
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="3">
-        <v>47</v>
-      </c>
-      <c r="D54" s="5" t="s">
+      <c r="A54" s="9">
+        <v>49.1345906617778</v>
+      </c>
+      <c r="D54" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E54" s="12">
+      <c r="E54" s="9">
         <f>C$32+E52</f>
-        <v>53.04003506231377</v>
+        <v>53.27993987137139</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="3">
-        <v>50</v>
-      </c>
-      <c r="D55" s="5" t="s">
+      <c r="A55" s="9">
+        <v>75.772494316589103</v>
+      </c>
+      <c r="D55" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E55" s="12">
+      <c r="E55" s="9">
         <f>C$32-E52</f>
-        <v>50.66366864138994</v>
+        <v>50.720060128628639</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="3">
-        <v>42</v>
+      <c r="A56" s="9">
+        <v>43.271309626006577</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="3">
-        <v>57</v>
+      <c r="A57" s="9">
+        <v>40.391241984616521</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="3">
-        <v>49</v>
+      <c r="A58" s="9">
+        <v>59.627415171962838</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="3">
-        <v>62</v>
+      <c r="A59" s="9">
+        <v>66.358063169849004</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="3">
-        <v>54</v>
+      <c r="A60" s="9">
+        <v>56.920422613214278</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="3">
-        <v>64</v>
+      <c r="A61" s="9">
+        <v>60.32114633858059</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="3">
-        <v>41</v>
+      <c r="A62" s="9">
+        <v>66.404367617701652</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="3">
-        <v>65</v>
+      <c r="A63" s="9">
+        <v>50.742505973776872</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="3">
-        <v>39</v>
+      <c r="A64" s="9">
+        <v>37.052741621384754</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" s="3">
-        <v>50</v>
+      <c r="A65" s="9">
+        <v>46.230016979357359</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" s="3">
-        <v>67</v>
+      <c r="A66" s="9">
+        <v>61.527209942183703</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" s="3">
-        <v>42</v>
+      <c r="A67" s="9">
+        <v>36.839303448539432</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" s="3">
-        <v>54</v>
+      <c r="A68" s="9">
+        <v>52.05653150907149</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" s="3">
-        <v>49</v>
+      <c r="A69" s="9">
+        <v>54.319796388905814</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" s="3">
-        <v>54</v>
+      <c r="A70" s="9">
+        <v>48.46009452043203</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" s="3">
-        <v>49</v>
+      <c r="A71" s="9">
+        <v>59.165487686303827</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" s="3">
-        <v>52</v>
+      <c r="A72" s="9">
+        <v>57.69391926295944</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" s="3">
-        <v>55</v>
+      <c r="A73" s="9">
+        <v>75.624714438399081</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" s="3">
-        <v>49</v>
+      <c r="A74" s="9">
+        <v>58.097608137863816</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" s="3">
-        <v>63</v>
+      <c r="A75" s="9">
+        <v>45.433446791508175</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" s="3">
-        <v>48</v>
+      <c r="A76" s="9">
+        <v>45.923850632932151</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" s="3">
-        <v>49</v>
+      <c r="A77" s="9">
+        <v>43.14472109745698</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" s="3">
-        <v>55</v>
+      <c r="A78" s="9">
+        <v>61.520800479061776</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" s="3">
-        <v>67</v>
+      <c r="A79" s="9">
+        <v>45.87198092766301</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" s="3">
-        <v>37</v>
+      <c r="A80" s="9">
+        <v>50.987334668583998</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" s="3">
-        <v>45</v>
+      <c r="A81" s="9">
+        <v>59.429929402684039</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" s="3">
-        <v>59</v>
+      <c r="A82" s="9">
+        <v>44.258481666731065</v>
       </c>
     </row>
   </sheetData>

--- a/M2_Statistica_&_Excel/W2_D1.xlsx
+++ b/M2_Statistica_&_Excel/W2_D1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SZN\Desktop\EPICODE CORSO\esercizi\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SZN\Desktop\EPICODE CORSO\esercizi\esercizi consegnati\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB822322-8FC3-4498-A463-385FFF718652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0B1475F-7BE6-4FAD-98FF-97035BC01473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B0536D41-C147-4827-AD61-53A4FD8EB59B}"/>
   </bookViews>
